--- a/data/Isotopes/output/mgs_intersections.xlsx
+++ b/data/Isotopes/output/mgs_intersections.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Isotopes/output/mgs_intersections.xlsx
+++ b/data/Isotopes/output/mgs_intersections.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U116"/>
+  <dimension ref="A1:U98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,7 +912,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>CU269</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -939,7 +939,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>CU431</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -966,7 +966,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>CU477</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -993,7 +993,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>CU478</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>EXMFT003</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1047,7 +1047,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>EXMFT013</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>EXMFT033</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>EXMFT050</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1128,7 +1128,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>EXMFT060</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>EXMFT070</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>EXMFT071</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>EXMFT096</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>EXMFT109</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1263,7 +1263,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>EXMFT112</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>EXMFT134</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>ICT005</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1344,7 +1344,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>ICT006</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>ISic000004</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>ISic000027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>ISic000028</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>ISic000034</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>ISic000036</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1506,7 +1506,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>ISic000068</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1533,7 +1533,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>ISic000069</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1560,67 +1560,147 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>ISic000107</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t xml:space="preserve">ISic000132 </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>ISic000139</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1628,38 +1708,90 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>ISic000151</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -1668,80 +1800,192 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>ISic000154</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>ISic000161</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>ISic000162</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -1749,67 +1993,159 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>ISic000163</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>ISic000164</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>ISic000172</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1818,37 +2154,85 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>ISic000178</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -1857,13 +2241,25 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>ISic000181</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -1875,7 +2271,11 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -1884,25 +2284,49 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>ISic000184</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -1911,10 +2335,14 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>ISic000195</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -1925,38 +2353,90 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>ISic000207</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -1965,13 +2445,21 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>ISic000208</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -1979,26 +2467,66 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>ISic000216</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -2010,7 +2538,11 @@
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -2019,13 +2551,25 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>ISic000220</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -2037,7 +2581,11 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -2046,25 +2594,49 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>ISic000227</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -2073,25 +2645,49 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>ISic000229</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -2100,25 +2696,49 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>ISic000232</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -2127,7 +2747,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>ISic000281</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2154,7 +2774,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>ISic000366</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2181,7 +2801,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>ISic000368</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2208,7 +2828,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>ISic000711</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2235,7 +2855,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>ISic000725</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2262,7 +2882,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>ISic000729</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2289,7 +2909,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>ISic000871</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2316,7 +2936,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>ISic001120</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2343,7 +2963,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>ISic001135</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2370,10 +2990,14 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>ISic001140</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -2384,26 +3008,66 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>ISic001143</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -2415,7 +3079,11 @@
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -2424,25 +3092,49 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>ISic001158</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>🔍🔍</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -2451,7 +3143,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>ISic001399</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2478,7 +3170,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>ISic003300</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2505,7 +3197,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>ISic003335</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2532,7 +3224,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>ISic004341</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2559,7 +3251,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>ISic004363</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2586,7 +3278,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>ISic004364</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2613,7 +3305,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>ISic004365</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2640,7 +3332,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>MARPO102146</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2667,7 +3359,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>MARPO102147</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2694,7 +3386,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>MARPO107187</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2721,7 +3413,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>MARPO14450</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2748,7 +3440,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MARPO15577</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2775,7 +3467,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>MARPO15585</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2802,7 +3494,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>MARPO176+162</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2829,7 +3521,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>MARPO252</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2856,7 +3548,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>MARPO253</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2883,7 +3575,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>MARPO254</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2910,7 +3602,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>MARPO33266</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -2937,7 +3629,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>MARPO5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2964,7 +3656,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>ORSI099</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2991,7 +3683,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>ORSI136</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3018,7 +3710,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>ORSI291</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3045,7 +3737,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>ORSI316</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3072,7 +3764,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>ORSI329</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3099,7 +3791,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>ORSI330</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3126,7 +3818,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>ORSI340</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3153,7 +3845,7 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>ORSI373</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3180,7 +3872,7 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>ORSI416</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3207,147 +3899,67 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>ISic000107</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+          <t>ORSI431</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISic000132 </t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+          <t>ORSI436</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>ISic000139</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+          <t>ORSI437</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
@@ -3355,90 +3967,38 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>ISic000151</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+          <t>SALINAS5644</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
@@ -3447,1102 +4007,56 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>ISic000154</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+          <t>SALINASTINDARI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>ISic000161</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="inlineStr">
-        <is>
-          <t>ISic000162</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
-        <is>
-          <t>ISic000163</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>ISic000164</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>ISic000172</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>ISic000178</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="inlineStr">
-        <is>
-          <t>ISic000181</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr">
-        <is>
-          <t>ISic000184</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="inlineStr">
-        <is>
-          <t>ISic000195</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="inlineStr">
-        <is>
-          <t>ISic000207</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="inlineStr">
-        <is>
-          <t>ISic000208</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr">
-        <is>
-          <t>ISic000216</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="inlineStr">
-        <is>
-          <t>ISic000220</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="inlineStr">
-        <is>
-          <t>ISic000227</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>ISic000229</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t>ISic000232</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="inlineStr">
-        <is>
-          <t>ISic001140</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="inlineStr">
-        <is>
-          <t>ISic001143</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
-      <c r="U115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="inlineStr">
-        <is>
-          <t>ISic001158</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>🔍🔍</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
-      <c r="U116" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
